--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_rf_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_rf_yearly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>0.6616703820773265</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -958,27 +959,27 @@
         <v>0.3840428795918789</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -986,11 +987,11 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
@@ -998,15 +999,15 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1095,27 +1096,27 @@
         <v>0.553572003431536</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1123,19 +1124,19 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
@@ -1143,7 +1144,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1236,27 +1237,27 @@
         <v>0.5954270081612255</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1266,51 +1267,51 @@
         <v>0.3643516266764959</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/7</t>
         </is>
       </c>
     </row>
@@ -1393,27 +1394,27 @@
         <v>0.7784056655317397</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1421,19 +1422,19 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
@@ -1441,7 +1442,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1534,27 +1535,27 @@
         <v>0.7070231503711849</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1564,19 +1565,19 @@
         <v>0.1534374836809493</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1584,31 +1585,31 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1691,19 +1692,19 @@
         <v>0.737047454264199</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
@@ -1711,7 +1712,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1719,19 +1720,19 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
@@ -1739,7 +1740,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1832,19 +1833,19 @@
         <v>0.6685586450323554</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z10" s="2" t="n">
@@ -1852,7 +1853,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="n">
@@ -1862,19 +1863,19 @@
         <v>0.02530364144366759</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH10" s="2" t="n">
@@ -1882,31 +1883,31 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -2151,28 +2152,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196766684</v>
+        <v>0.05644008609220896</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208207</v>
+        <v>0.08831268540851259</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571159</v>
+        <v>0.2970580221997939</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798217</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2181,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278889</v>
+        <v>0.2724034021441999</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -2193,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1395291740668931</v>
+        <v>-0.08310591627223018</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2239,49 +2240,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.1051693667903664</v>
+        <v>0.08494274132399737</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.01294764165236018</v>
+        <v>0.02697990696019525</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.3008863680359475</v>
+        <v>0.09182038001016277</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1971883490136813</v>
+        <v>0.3163123058422522</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.5165540962256934</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.08704754021851291</v>
+        <v>-0.007563205902741954</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.097979358321054</v>
+        <v>1.036997366224467</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.8509426312718931</v>
+        <v>0.3166911337044074</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.08116512286290178</v>
+        <v>0.0348063605343838</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.195162867761455</v>
+        <v>1.162581418629872</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1452618683874185</v>
+        <v>-0.09650539287730475</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2333,58 +2334,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.2778810924357364</v>
+        <v>0.05780006109971869</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.409580203409349</v>
+        <v>0.00128731863303333</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1114259070568875</v>
+        <v>0.08435250706252208</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1527123066850303</v>
+        <v>0.2776876941001362</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9584487534626038</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2517736539689071</v>
+        <v>-0.1629630992012946</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.412971084767529</v>
+        <v>0.008148606170506056</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5351661656481069</v>
+        <v>0.9601389978554115</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.7078803749883373</v>
+        <v>0.2637436415173093</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.002399823602007745</v>
+        <v>-0.00680582951310682</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.9942295848294278</v>
+        <v>0.9682097926871471</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1157994371504594</v>
+        <v>-0.05511881647811512</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.4280703465103266</v>
+        <v>-0.02501761539153247</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.5476940443379932</v>
+        <v>0.01583154934067088</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.07729156693811146</v>
+        <v>-0.04021253795347923</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2435,58 +2436,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.03458152166138273</v>
+        <v>0.08494274132399737</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.141206048340013</v>
+        <v>0.02697990696019525</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2317017928095088</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1728427729059527</v>
+        <v>0.09182038001016277</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1085826557182779</v>
+        <v>0.3163123058422522</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9950138504155125</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1841625042417996</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.5406498280770047</v>
+        <v>-0.007563205902741954</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.3914529566441791</v>
+        <v>1.036997366224467</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2317017928095088</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2681220549931846</v>
+        <v>0.3166911337044074</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.25926967469017</v>
+        <v>0.0348063605343838</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.3765818192429461</v>
+        <v>1.162581418629872</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.07784236084278906</v>
+        <v>-0.09650539287730475</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.1561757982630545</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.6875466094321661</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.3148777095691062</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2541,67 +2542,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.006255495104017572</v>
+        <v>0.08494274132399737</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.096160346717584</v>
+        <v>0.02697990696019525</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4634241885131012</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.2485407316216583</v>
+        <v>0.09182038001016277</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1705822430493028</v>
+        <v>0.3163123058422522</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.4222074131701598</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.09111931504971338</v>
+        <v>-0.007563205902741954</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8974375152150924</v>
+        <v>1.036997366224467</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4634241885131012</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.7198983295170589</v>
+        <v>0.3166911337044074</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.004620055385639477</v>
+        <v>0.0348063605343838</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.011108998871365</v>
+        <v>1.162581418629872</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1157994371504594</v>
+        <v>-0.09650539287730475</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1105392104554561</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1951545815549587</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.07079868362250963</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.2223497860807757</v>
+        <v>0.02565955630221883</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.2277836915330568</v>
+        <v>-0.01558481753293295</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.007036765984739235</v>
+        <v>0.04189733617454783</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -2649,49 +2650,49 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.1051693667903664</v>
+        <v>0.08494274132399737</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.01294764165236018</v>
+        <v>0.02697990696019525</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.3008863680359475</v>
+        <v>0.09182038001016277</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1971883490136813</v>
+        <v>0.3163123058422522</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.5165540962256934</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.08704754021851291</v>
+        <v>-0.007563205902741954</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.097979358321054</v>
+        <v>1.036997366224467</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.8509426312718931</v>
+        <v>0.3166911337044074</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.08116512286290178</v>
+        <v>0.0348063605343838</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.195162867761455</v>
+        <v>1.162581418629872</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1452618683874185</v>
+        <v>-0.09650539287730475</v>
       </c>
       <c r="Y7" s="2" t="n">
         <v>0</v>
@@ -2755,49 +2756,49 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.1051693667903664</v>
+        <v>0.08494274132399737</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.01294764165236018</v>
+        <v>0.02697990696019525</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.3008863680359475</v>
+        <v>0.09182038001016277</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1971883490136813</v>
+        <v>0.3163123058422522</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.5165540962256934</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.08704754021851291</v>
+        <v>-0.007563205902741954</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.097979358321054</v>
+        <v>1.036997366224467</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.8509426312718931</v>
+        <v>0.3166911337044074</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.08116512286290178</v>
+        <v>0.0348063605343838</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.195162867761455</v>
+        <v>1.162581418629872</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1452618683874185</v>
+        <v>-0.09650539287730475</v>
       </c>
       <c r="Y8" s="2" t="n">
         <v>0</v>
@@ -2809,13 +2810,13 @@
         <v>0</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.2997543836382931</v>
+        <v>0.02565955630221883</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.3538774645684332</v>
+        <v>-0.01558481753293295</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.08376597001680097</v>
+        <v>0.04189733617454783</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -2863,64 +2864,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.2134953611554679</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.1324377711139624</v>
+        <v>-0.03796582501302292</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.4767451185382657</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.3225652770054991</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1596388080614179</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.470410219361051</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>9.181820512593752e-05</v>
+        <v>0.2117597153840098</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.9998966508554079</v>
+        <v>-0.03587709265072057</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.4767451185382657</v>
+        <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4851204981629664</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1325174218072699</v>
+        <v>-0.2060850325577082</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6813596880528829</v>
+        <v>0.03737143334716829</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1028029799877935</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1210575390971487</v>
+        <v>-0.06323953519738668</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.09544785984200699</v>
+        <v>0.2209943470367326</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1976409894765612</v>
+        <v>-0.2327888600990946</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.2618004968622551</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.1860700172543425</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2969,70 +2974,74 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.1482244678213634</v>
+        <v>0.05780006109971869</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.06044002449480756</v>
+        <v>0.00128731863303333</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.5065899861024923</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.3104897299760587</v>
+        <v>0.08435250706252208</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1820020608095362</v>
+        <v>0.2776876941001362</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.5006164103140791</v>
+        <v>-0.1629630992012946</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-0.05695037848306939</v>
+        <v>0.008148606170506056</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.0641024608611</v>
+        <v>0.9601389978554115</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.5065899861024923</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.7056538295828798</v>
+        <v>0.2637436415173093</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.003700384298044535</v>
+        <v>-0.00680582951310682</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.9911023653269683</v>
+        <v>0.9682097926871471</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1359328483814991</v>
+        <v>-0.05511881647811512</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.04811536332474942</v>
+        <v>-0.02501761539153247</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.03296684445392395</v>
+        <v>0.01583154934067088</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.07849449206817216</v>
+        <v>-0.04021253795347923</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.3334469558860997</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.3325768434446857</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.001303689320437784</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.2618004968622551</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>-0.004787352809128453</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3275,28 +3284,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.0534149946425504</v>
+        <v>-0.09123360655355228</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2216991067360385</v>
+        <v>0.2716992530341478</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389480542019929</v>
+        <v>0.1810585772249195</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.5035092528573141</v>
+        <v>-0.4707583434268607</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3305,10 +3314,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.121721302370637</v>
+        <v>0.717110477150922</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -3317,7 +3326,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756414</v>
+        <v>-0.1395291740668931</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3363,49 +3372,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.0368407257795742</v>
+        <v>-0.1038483060444678</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.01573384558532909</v>
+        <v>-0.01388112454629287</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.514605350956002</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.2138025395451635</v>
+        <v>0.3010407489256601</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2486051666650726</v>
+        <v>0.1972971759393627</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9898255813953488</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.5129198176356869</v>
+        <v>-0.5164822477237525</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.01895415943304257</v>
+        <v>-0.08639513486703954</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.018689954007736</v>
+        <v>1.097128186755113</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.514605350956002</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.128685919321732</v>
+        <v>0.8533997764026979</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.003282531472589278</v>
+        <v>0.07937130491330469</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.006208865728391</v>
+        <v>1.190053420768935</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.204891821182839</v>
+        <v>-0.1452618683874185</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3457,58 +3466,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.1975871140978549</v>
+        <v>0.2834444878548723</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.1368616548924535</v>
+        <v>0.412293078958915</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1847647558521955</v>
+        <v>0.1114874581688012</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2118271660599822</v>
+        <v>0.1527921426208967</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9614825581395349</v>
+        <v>0.9584026622296173</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.2500855498878848</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07708757922255405</v>
+        <v>0.4169603635659389</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.9239869583598836</v>
+        <v>0.5312397610786888</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.239468393809461</v>
+        <v>0.711454536798154</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.05549602170052359</v>
+        <v>-0.003293870969882207</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.104970005642202</v>
+        <v>0.9921128744691625</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1247701957278803</v>
+        <v>-0.1157994371504594</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.1550347939867232</v>
+        <v>0.432173254273353</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.09789729968183036</v>
+        <v>0.5509553611666933</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.05204265856328316</v>
+        <v>-0.0765864123929314</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -3559,58 +3568,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.01355385902928785</v>
+        <v>0.03610890012382595</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.03783991666720898</v>
+        <v>0.1401267780099555</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.08092115510307485</v>
+        <v>-0.2317017928095088</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.03836768391138675</v>
+        <v>0.1729385543630289</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.04698937468166735</v>
+        <v>0.1086417117972056</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9934593023255814</v>
+        <v>0.9950083194675541</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.03602202520150855</v>
+        <v>-0.1840412565459567</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.9415829607020951</v>
+        <v>0.5417507925158584</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.0715419329378572</v>
+        <v>0.390946350958409</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.08092115510307485</v>
+        <v>-0.2317017928095088</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.0514284408221668</v>
+        <v>0.269805499893123</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.5044455463366526</v>
+        <v>-0.260498659352414</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.04584778831736398</v>
+        <v>0.3762397963631203</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.02143379927073719</v>
+        <v>-0.07784236084278906</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.02245944451379223</v>
+        <v>0.1561757982630545</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.9790950436934043</v>
+        <v>0.6875466094321658</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.5060668972916464</v>
+        <v>-0.3148777095691061</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -3665,67 +3674,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1577793538198262</v>
+        <v>-0.004788405346303648</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.09907240708367659</v>
+        <v>0.09512367736158223</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4679611464684285</v>
+        <v>-0.4634241885131011</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1877581549228757</v>
+        <v>0.2486780986034204</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2131069073459811</v>
+        <v>0.1706761531747413</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9665697674418605</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.4661136411094471</v>
+        <v>-0.4221215431038875</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.07531985633786631</v>
+        <v>0.09189904029455742</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.9257300406384701</v>
+        <v>0.896684145906105</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4679611464684285</v>
+        <v>-0.4634241885131011</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.168587630194859</v>
+        <v>0.7221815120071335</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.02208882371678955</v>
+        <v>0.002953237385532326</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.041780723719141</v>
+        <v>1.007071483429385</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1247701957278803</v>
+        <v>-0.1157994371504594</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1166414715715582</v>
+        <v>0.1105392104554561</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.09609542375351876</v>
+        <v>0.1951545815549582</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.0187447619730774</v>
+        <v>-0.07079868362250941</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.03323997044508609</v>
+        <v>-0.2245776080918962</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.001641206266591477</v>
+        <v>-0.2294074920016311</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.03165070952130289</v>
+        <v>0.006267753526802977</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -3773,58 +3782,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3142064924795651</v>
+        <v>-0.1038483060444678</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.2475676719653186</v>
+        <v>-0.01388112454629287</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2738128049668617</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.07954739255315829</v>
+        <v>0.3010407489256601</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1685750568475212</v>
+        <v>0.1972971759393627</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9476744186046512</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2712911193314199</v>
+        <v>-0.5164822477237525</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4677189552117822</v>
+        <v>-0.08639513486703954</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5388006631296192</v>
+        <v>1.097128186755113</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2738128049668617</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.8034725901429927</v>
+        <v>0.8533997764026979</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1499955304554181</v>
+        <v>0.07937130491330469</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7162853985610687</v>
+        <v>1.190053420768935</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.204891821182839</v>
+        <v>-0.1452618683874185</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.2675104862335018</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.4960758147280566</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1527765680351578</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3879,67 +3888,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.0768866771845309</v>
+        <v>-0.1038483060444678</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.02228151551036639</v>
+        <v>-0.01388112454629287</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4757042557897395</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1718832247584118</v>
+        <v>0.3010407489256601</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2334481106125792</v>
+        <v>0.1972971759393627</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9803779069767442</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4738836383842814</v>
+        <v>-0.5164822477237525</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.05967002334591065</v>
+        <v>-0.08639513486703954</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.941161727803584</v>
+        <v>1.097128186755113</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.4757042557897395</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.046860268472511</v>
+        <v>0.8533997764026979</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.03528316080650273</v>
+        <v>0.07937130491330469</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.9332623587160958</v>
+        <v>1.190053420768935</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.204891821182839</v>
+        <v>-0.1452618683874185</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.03862305020363399</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.08014323034437965</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03843951336667484</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.1007863524018024</v>
+        <v>-0.301760455994988</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.01617097459169992</v>
+        <v>-0.3552361176612083</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>-0.08600618158727946</v>
+        <v>0.08293836415316047</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -3987,58 +3996,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.2372455231194361</v>
+        <v>-0.2123342247724661</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.1745091245252912</v>
+        <v>-0.1332582488659668</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2048918211828392</v>
+        <v>-0.4767451185382658</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.06242636374223392</v>
+        <v>0.32270136157811</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1468645482209767</v>
+        <v>0.1597267491786882</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9556686046511628</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.03602202520150877</v>
+        <v>-0.4703315130733674</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.9415829607020947</v>
+        <v>0.0008064942511463169</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.07154193293785764</v>
+        <v>0.9990933132477563</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.08092115510307474</v>
+        <v>-0.4767451185382658</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.2834790373484088</v>
+        <v>0.4870920106988315</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.3950765183370903</v>
+        <v>-0.1339567078023679</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2527178870092834</v>
+        <v>0.6792426358544456</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.2048918211828392</v>
+        <v>-0.1028029799877935</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1932840718512312</v>
+        <v>-0.1210575390971491</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.9790950436934038</v>
+        <v>0.0954478598420061</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.3970557019715868</v>
+        <v>-0.1976409894765612</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -4093,67 +4102,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.04214784511765468</v>
+        <v>-0.1469669703932278</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.01069583173032285</v>
+        <v>-0.06132859252014122</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.4679611464684285</v>
+        <v>-0.5065899861024923</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1986558256130265</v>
+        <v>0.3106394045895665</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2297783815570869</v>
+        <v>0.1821024428541336</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9869186046511628</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.4661136411094471</v>
+        <v>-0.5005421931937507</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.07531985633786631</v>
+        <v>-0.0562764653858534</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.9257300406384701</v>
+        <v>1.063267810720209</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.4679611464684285</v>
+        <v>-0.5065899861024923</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.9520031328076992</v>
+        <v>0.7079181023547045</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.0799907930289</v>
+        <v>-0.005353397418825234</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.8486984519200477</v>
+        <v>0.9871813687163814</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.2048918211828387</v>
+        <v>-0.1359328483814991</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.005118548303636672</v>
+        <v>-0.04811536332474931</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.09609542375351876</v>
+        <v>0.03296684445392351</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.08300087152844471</v>
+        <v>-0.07849449206817205</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.1297937053182916</v>
+        <v>-0.3353565053424965</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.001641206266591477</v>
+        <v>-0.3339802870426375</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.128363169489866</v>
+        <v>-0.002066332682178929</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -4399,28 +4408,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093225</v>
+        <v>0.0534149946425504</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.08126757478702552</v>
+        <v>0.2216991067360385</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962864</v>
+        <v>0.2389480542019929</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573141</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4429,10 +4438,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165614</v>
+        <v>1.121721302370637</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4441,7 +4450,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756414</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4487,49 +4496,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.05350828208151159</v>
+        <v>0.0368407257795742</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.02940992881154214</v>
+        <v>-0.01573384558532909</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.514605350956002</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.06099826392968127</v>
+        <v>0.2138025395451635</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1970235800584944</v>
+        <v>0.2486051666650726</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.8689655172413793</v>
+        <v>0.9898255813953488</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.5129198176356869</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.02467166685502487</v>
+        <v>-0.01895415943304257</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8984331176243276</v>
+        <v>1.018689954007736</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.514605350956002</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2778889047779733</v>
+        <v>1.128685919321732</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.004624175830937105</v>
+        <v>0.003282531472589278</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.021624389692979</v>
+        <v>1.006208865728391</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.02931693909409494</v>
+        <v>-0.204891821182839</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4581,58 +4590,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.01678534845024493</v>
+        <v>0.1975871140978549</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.006472990324530081</v>
+        <v>0.1368616548924535</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04633586591900118</v>
+        <v>0.1847647558521955</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1676448275252702</v>
+        <v>0.2118271660599822</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9614825581395349</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.06089581754970363</v>
+        <v>0.07708757922255405</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7493076420581847</v>
+        <v>0.9239869583598836</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1912321754103152</v>
+        <v>1.239468393809461</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06350181305251279</v>
+        <v>0.05549602170052359</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7030415793294013</v>
+        <v>1.104970005642202</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02330447460112972</v>
+        <v>-0.1247701957278803</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.03485775504176369</v>
+        <v>0.1550347939867232</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.03535195894101339</v>
+        <v>0.09789729968183036</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.06781241236515334</v>
+        <v>0.05204265856328316</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4683,58 +4692,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.05350828208151137</v>
+        <v>0.01355385902928785</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.02940992881154192</v>
+        <v>-0.03783991666720898</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1829503201425124</v>
+        <v>-0.08092115510307485</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.06099826392968127</v>
+        <v>0.03836768391138675</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1970235800584944</v>
+        <v>0.04698937468166735</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8689655172413793</v>
+        <v>0.9934593023255814</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1755869558437452</v>
+        <v>-0.03602202520150855</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.02467166685502487</v>
+        <v>0.9415829607020951</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.8984331176243283</v>
+        <v>0.0715419329378572</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1829503201425124</v>
+        <v>-0.08092115510307485</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2778889047779733</v>
+        <v>0.0514284408221668</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.004624175830937105</v>
+        <v>-0.5044455463366526</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.021624389692979</v>
+        <v>0.04584778831736398</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.02931693909409516</v>
+        <v>-0.02143379927073719</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-0.02245944451379223</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0.9790950436934043</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>-0.5060668972916464</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -4789,67 +4798,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.05350828208151159</v>
+        <v>0.1577793538198262</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.02940992881154214</v>
+        <v>0.09907240708367659</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.4679611464684285</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.06099826392968127</v>
+        <v>0.1877581549228757</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1970235800584944</v>
+        <v>0.2131069073459811</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.8689655172413793</v>
+        <v>0.9665697674418605</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.4661136411094471</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.02467166685502487</v>
+        <v>0.07531985633786631</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8984331176243276</v>
+        <v>0.9257300406384701</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.4679611464684285</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2778889047779733</v>
+        <v>1.168587630194859</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.004624175830937105</v>
+        <v>0.02208882371678955</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.021624389692979</v>
+        <v>1.041780723719141</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.02931693909409494</v>
+        <v>-0.1247701957278803</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0</v>
+        <v>0.1166414715715582</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.09609542375351876</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
+        <v>0.0187447619730774</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.03611670219996643</v>
+        <v>-0.03323997044508609</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.03414487086804019</v>
+        <v>-0.001641206266591477</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.07274545731423809</v>
+        <v>-0.03165070952130289</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -4897,58 +4906,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.1031971660034978</v>
+        <v>0.3142064924795651</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1237109786376593</v>
+        <v>0.2475676719653186</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.2738128049668617</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.09597508479514891</v>
+        <v>0.07954739255315829</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1679324230140697</v>
+        <v>0.1685750568475212</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.9476744186046512</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.2712911193314199</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.02467166685502487</v>
+        <v>0.4677189552117822</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.8984331176243276</v>
+        <v>0.5388006631296192</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.2738128049668617</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.08780767159541325</v>
+        <v>0.8034725901429927</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1448099428259864</v>
+        <v>-0.1499955304554181</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3228141079461194</v>
+        <v>0.7162853985610687</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0</v>
+        <v>-0.204891821182839</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.1487462896593392</v>
+        <v>0.2675104862335018</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.4960758147280566</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1487462896593391</v>
+        <v>-0.1527765680351578</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -5003,67 +5012,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.008769501857632478</v>
+        <v>0.0768866771845309</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.03144328916664807</v>
+        <v>0.02228151551036639</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.4757042557897395</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.06989961147309434</v>
+        <v>0.1718832247584118</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1859762297433602</v>
+        <v>0.2334481106125792</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.9803779069767442</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.4738836383842814</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.02467166685502487</v>
+        <v>0.05967002334591065</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.8984331176243276</v>
+        <v>0.941161727803584</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.4757042557897395</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.2023469366097206</v>
+        <v>1.046860268472511</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.05476384078609708</v>
+        <v>-0.03528316080650273</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7439036322278363</v>
+        <v>0.9332623587160958</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.204891821182839</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.05911466003484678</v>
+        <v>0.03862305020363399</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>0.08014323034437965</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.05911466003484689</v>
+        <v>-0.03843951336667484</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.02513298440701117</v>
+        <v>-0.1007863524018024</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.03414487086804019</v>
+        <v>-0.01617097459169992</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.009330474301180613</v>
+        <v>-0.08600618158727946</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -5111,58 +5120,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.1031971660034983</v>
+        <v>0.2372455231194361</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.1237109786376598</v>
+        <v>0.1745091245252912</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1829503201425129</v>
+        <v>-0.2048918211828392</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.09597508479514935</v>
+        <v>0.06242636374223392</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1679324230140695</v>
+        <v>0.1468645482209767</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.9556686046511628</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1755869558437456</v>
+        <v>-0.03602202520150877</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.0246716668550242</v>
+        <v>0.9415829607020947</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.8984331176243305</v>
+        <v>0.07154193293785764</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1829503201425129</v>
+        <v>-0.08092115510307474</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.08780767159541325</v>
+        <v>0.2834790373484088</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1448099428259864</v>
+        <v>-0.3950765183370903</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.3228141079461194</v>
+        <v>0.2527178870092834</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0</v>
+        <v>-0.2048918211828392</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1487462896593397</v>
+        <v>0.1932840718512312</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>-6.661338147750939e-16</v>
+        <v>0.9790950436934038</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1487462896593391</v>
+        <v>-0.3970557019715868</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5217,67 +5226,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.008769501857632478</v>
+        <v>0.04214784511765468</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.03144328916664807</v>
+        <v>-0.01069583173032285</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.4679611464684285</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.06989961147309434</v>
+        <v>0.1986558256130265</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1859762297433602</v>
+        <v>0.2297783815570869</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.9869186046511628</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.4661136411094471</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.02467166685502487</v>
+        <v>0.07531985633786631</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.8984331176243276</v>
+        <v>0.9257300406384701</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.4679611464684285</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.2023469366097206</v>
+        <v>0.9520031328076992</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.05476384078609708</v>
+        <v>-0.0799907930289</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.7439036322278363</v>
+        <v>0.8486984519200477</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.2048918211828387</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.05911466003484678</v>
+        <v>0.005118548303636672</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0</v>
+        <v>0.09609542375351876</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.05911466003484689</v>
+        <v>-0.08300087152844471</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.02513298440701117</v>
+        <v>-0.1297937053182916</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.03414487086804019</v>
+        <v>-0.001641206266591477</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.009330474301180613</v>
+        <v>-0.128363169489866</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -5523,28 +5532,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714512</v>
+        <v>0.01891210187562642</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570336</v>
+        <v>0.08099293800751969</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.459050197355985</v>
+        <v>0.2138559415886579</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606707</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -5553,10 +5562,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473776</v>
+        <v>0.2720069211165614</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5565,7 +5574,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.05185156587886031</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5611,49 +5620,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.03395357056649728</v>
+        <v>0.05021558177844221</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.05818123641143114</v>
+        <v>0.03072245372804194</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1251027258735238</v>
+        <v>0.06079370905413644</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4741154654082622</v>
+        <v>0.1963965378157337</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.8904109589041096</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3121003427249628</v>
+        <v>-0.1781636276426457</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.03082746164398775</v>
+        <v>0.02597815036206796</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.075393689637123</v>
+        <v>0.8954168565455383</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.5030587086818397</v>
+        <v>0.2778889047779733</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.02822384424329949</v>
+        <v>0.004624175830937105</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9201515377292117</v>
+        <v>1.021624389692979</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.06371665664689741</v>
+        <v>-0.02931693909409494</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5705,58 +5714,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.003752373695923961</v>
+        <v>0.01712918805183983</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.0856912278706744</v>
+        <v>-0.001749821030199383</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.04617799198161064</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4277127620168583</v>
+        <v>0.167065999353103</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.06593925421638414</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.7345409743619887</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4142266877546186</v>
+        <v>0.1912321754103152</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08565662401838847</v>
+        <v>-0.06350181305251279</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7576676780024697</v>
+        <v>0.7030415793294013</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07121447292125116</v>
+        <v>-0.02330447460112972</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.02920943234813367</v>
+        <v>-0.03150438281497758</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.03176897285967573</v>
+        <v>0.03894927376398205</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.05910083246523712</v>
+        <v>-0.06781241236515334</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5807,55 +5816,55 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.03395357056649728</v>
+        <v>0.05021558177844199</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.05818123641143114</v>
+        <v>0.03072245372804172</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425126</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1251027258735238</v>
+        <v>0.06079370905413644</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4741154654082621</v>
+        <v>0.1963965378157337</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.8904109589041096</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3121003427249628</v>
+        <v>-0.1781636276426458</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.03082746164398775</v>
+        <v>0.02597815036206774</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.075393689637123</v>
+        <v>0.8954168565455388</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425126</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.5030587086818397</v>
+        <v>0.2778889047779733</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.02822384424329949</v>
+        <v>0.004624175830937105</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9201515377292117</v>
+        <v>1.021624389692979</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.06371665664689741</v>
+        <v>-0.02931693909409516</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0</v>
@@ -5913,49 +5922,49 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.03395357056649728</v>
+        <v>0.05021558177844221</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.05818123641143114</v>
+        <v>0.03072245372804194</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1251027258735238</v>
+        <v>0.06079370905413644</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4741154654082622</v>
+        <v>0.1963965378157337</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.8904109589041096</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3121003427249628</v>
+        <v>-0.1781636276426457</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.03082746164398775</v>
+        <v>0.02597815036206796</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.075393689637123</v>
+        <v>0.8954168565455383</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.5030587086818397</v>
+        <v>0.2778889047779733</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.02822384424329949</v>
+        <v>0.004624175830937105</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9201515377292117</v>
+        <v>1.021624389692979</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.06371665664689741</v>
+        <v>-0.02931693909409494</v>
       </c>
       <c r="Y6" s="2" t="n">
         <v>0</v>
@@ -5967,13 +5976,13 @@
         <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.03008829434631299</v>
+        <v>0.03252919502779639</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.03079078136225011</v>
+        <v>-0.03748910052448828</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.06281314141247085</v>
+        <v>0.07274545731423809</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -6021,58 +6030,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.03395357056649728</v>
+        <v>-0.1060000893535255</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.05818123641143114</v>
+        <v>-0.1225936869325743</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1251027258735238</v>
+        <v>0.09565016416329207</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4741154654082622</v>
+        <v>0.1673815319423042</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.9794520547945206</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3121003427249628</v>
+        <v>-0.1781636276426457</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.03082746164398775</v>
+        <v>0.02597815036206796</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.075393689637123</v>
+        <v>0.8954168565455383</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.5030587086818397</v>
+        <v>0.08780767159541325</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.02822384424329949</v>
+        <v>-0.1448099428259864</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.9201515377292117</v>
+        <v>0.3228141079461194</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.06371665664689741</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1487462896593392</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1487462896593391</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6127,67 +6136,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.03395357056649728</v>
+        <v>-0.01186755530168937</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.05818123641143114</v>
+        <v>-0.03020835371437458</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1251027258735238</v>
+        <v>0.06966431104098045</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4741154654082622</v>
+        <v>0.1853776939495975</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.9794520547945206</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.3121003427249628</v>
+        <v>-0.1781636276426457</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.03082746164398775</v>
+        <v>0.02597815036206796</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.075393689637123</v>
+        <v>0.8954168565455383</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.5030587086818397</v>
+        <v>0.2023469366097206</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.02822384424329949</v>
+        <v>-0.05476384078609708</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.9201515377292117</v>
+        <v>0.7439036322278363</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.06371665664689741</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0</v>
+        <v>-0.05911466003484689</v>
       </c>
       <c r="Z8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0</v>
+        <v>-0.05911466003484689</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.03008829434631299</v>
+        <v>-0.02850841731232601</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.03079078136225011</v>
+        <v>-0.03748910052448828</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.06281314141247085</v>
+        <v>0.009330474301180613</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -6235,58 +6244,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.03395357056649662</v>
+        <v>-0.106000089353526</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.0581812364114318</v>
+        <v>-0.1225936869325749</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.312100342724963</v>
+        <v>-0.1829503201425129</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.125102725873524</v>
+        <v>0.0956501641632925</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4741154654082621</v>
+        <v>0.167381531942304</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.9794520547945206</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.312100342724963</v>
+        <v>-0.1781636276426463</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-0.03082746164398809</v>
+        <v>0.0259781503620673</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.075393689637124</v>
+        <v>0.895416856545541</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.312100342724963</v>
+        <v>-0.1829503201425129</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.5030587086818388</v>
+        <v>0.08780767159541325</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.02822384424330004</v>
+        <v>-0.1448099428259864</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.9201515377292101</v>
+        <v>0.3228141079461194</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.06371665664689741</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2" t="n">
+        <v>-0.1487462896593398</v>
+      </c>
+      <c r="Z9" s="2" t="n">
         <v>-6.661338147750939e-16</v>
       </c>
-      <c r="Z9" s="2" t="n">
-        <v>-3.33066907387547e-16</v>
-      </c>
       <c r="AA9" s="2" t="n">
-        <v>-5.551115123125783e-16</v>
+        <v>-0.1487462896593391</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -6341,67 +6350,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.03395357056649728</v>
+        <v>-0.01186755530168937</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.05818123641143114</v>
+        <v>-0.03020835371437458</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1251027258735238</v>
+        <v>0.06966431104098045</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4741154654082622</v>
+        <v>0.1853776939495975</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.9794520547945206</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.3121003427249628</v>
+        <v>-0.1781636276426457</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-0.03082746164398775</v>
+        <v>0.02597815036206796</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.075393689637123</v>
+        <v>0.8954168565455383</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.5030587086818397</v>
+        <v>0.2023469366097206</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.02822384424329949</v>
+        <v>-0.05476384078609708</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.9201515377292117</v>
+        <v>0.7439036322278363</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.06371665664689741</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0</v>
+        <v>-0.05911466003484689</v>
       </c>
       <c r="Z10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>0</v>
+        <v>-0.05911466003484689</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.03008829434631299</v>
+        <v>-0.02850841731232601</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.03079078136225011</v>
+        <v>-0.03748910052448828</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.06281314141247085</v>
+        <v>0.009330474301180613</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -6647,28 +6656,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393744</v>
+        <v>0.1113578145363057</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1799741913752893</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2405796270435321</v>
+        <v>0.4518304992174231</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450099</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -6677,10 +6686,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241682997</v>
+        <v>0.5657770181230004</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -6689,7 +6698,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174769</v>
+        <v>-0.05185156587886031</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6735,49 +6744,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.2930599188275502</v>
+        <v>0.04161196027515435</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.2186985464363551</v>
+        <v>-0.06275733463056765</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1617038815488626</v>
+        <v>0.1231169123948052</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.244271120885344</v>
+        <v>0.466550204870466</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9317738791423001</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3268135676014445</v>
+        <v>-0.3121003427249628</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.02460593955894141</v>
+        <v>-0.03082746164398775</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.054811272550568</v>
+        <v>1.075393689637123</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.9208050795385059</v>
+        <v>0.5141917127874007</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.2494422468446016</v>
+        <v>-0.0329454990963135</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.713667649530219</v>
+        <v>0.9088239647719573</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1128970535188779</v>
+        <v>-0.06371665664689741</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6829,58 +6838,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.09480060127513035</v>
+        <v>0.006687707983713542</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.03184073837926271</v>
+        <v>-0.09418218433661163</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1155318330023982</v>
+        <v>0.1158491063192834</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1720647483703307</v>
+        <v>0.4208473686607196</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1036687135184475</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.769071443176754</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4372788934221374</v>
+        <v>0.4183623971148742</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06508110111248899</v>
+        <v>-0.09414790184163113</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.813799478447114</v>
+        <v>0.7394474920575899</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.08016850348153992</v>
+        <v>-0.07121447292125116</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.1533257002755035</v>
+        <v>-0.03352904308262272</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1315105948250137</v>
+        <v>0.03176897285967573</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2517310013739348</v>
+        <v>-0.06328743901003064</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -6931,68 +6940,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.1204198572323685</v>
+        <v>0.04161196027515435</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.05598668052877809</v>
+        <v>-0.06275733463056765</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.01059279431847393</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0007071954500480373</v>
+        <v>0.1231169123948052</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0210064258419617</v>
+        <v>0.466550204870466</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.01364522417153996</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.3121003427249628</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.4652994336443077</v>
+        <v>-0.03082746164398775</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.03648365119369596</v>
+        <v>1.075393689637123</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1078964420679485</v>
+        <v>0.5141917127874007</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2793372765439067</v>
+        <v>-0.0329454990963135</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.2008010667837793</v>
+        <v>0.9088239647719573</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.01059279431847393</v>
+        <v>-0.06371665664689741</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.1335128087116944</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.5022640521121498</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.4232124571775224</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.3731056573317193</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.2713930824850518</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7041,74 +7046,70 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1145658085070207</v>
+        <v>0.04161196027515435</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.05046928681138718</v>
+        <v>-0.06275733463056765</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.115533569251825</v>
+        <v>0.1231169123948052</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1729444590617458</v>
+        <v>0.466550204870466</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9454191033138402</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2382824194485824</v>
+        <v>-0.3121003427249628</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1036687135184464</v>
+        <v>-0.03082746164398775</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7690714431767565</v>
+        <v>1.075393689637123</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4632271027539783</v>
+        <v>0.5141917127874007</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.04820235099123316</v>
+        <v>-0.0329454990963135</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.862090488003121</v>
+        <v>0.9088239647719573</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.08016850348153992</v>
+        <v>-0.06371665664689741</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.1380400921268788</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1315105948250126</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.2382219735145982</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.01805370513029447</v>
+        <v>0.03469224071623001</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>-0.03079078136225011</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.01805370513029558</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.3731056573317193</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.09817014575252636</v>
-      </c>
+        <v>0.06756335042966111</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7153,58 +7154,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.2043375826494194</v>
+        <v>0.04161196027515435</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.2500945877601592</v>
+        <v>-0.06275733463056765</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.2359673144875147</v>
+        <v>0.1231169123948052</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1972033968639685</v>
+        <v>0.466550204870466</v>
       </c>
       <c r="O7" s="2" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="P7" t="b">
-        <v>0</v>
-      </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3268135676014445</v>
+        <v>-0.3121003427249628</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.02460593955894141</v>
+        <v>-0.03082746164398775</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.054811272550568</v>
+        <v>1.075393689637123</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1819347198006422</v>
+        <v>0.5141917127874007</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2311769748723456</v>
+        <v>-0.0329454990963135</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3385902734213445</v>
+        <v>0.9088239647719573</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.07668379937247682</v>
+        <v>-0.06371665664689741</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.3846670167674614</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.3846670167674615</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -7259,67 +7260,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.03394881166061836</v>
+        <v>0.04161196027515435</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.08950454509499595</v>
+        <v>-0.06275733463056765</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1952303144959528</v>
+        <v>0.1231169123948052</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2151016248349985</v>
+        <v>0.466550204870466</v>
       </c>
       <c r="O8" s="2" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.3268135676014445</v>
+        <v>-0.3121003427249628</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.02460593955894141</v>
+        <v>-0.03082746164398775</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.054811272550568</v>
+        <v>1.075393689637123</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4350425704471679</v>
+        <v>0.5141917127874007</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.06653578094038048</v>
+        <v>-0.0329454990963135</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.8096375614233425</v>
+        <v>0.9088239647719573</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.08016850348153992</v>
+        <v>-0.06371665664689741</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.2528952647334979</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.2528952647334979</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.1176007875642308</v>
+        <v>0.03469224071623001</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.1162256857571463</v>
+        <v>-0.03079078136225011</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>-0.001555942263679166</v>
+        <v>0.06756335042966111</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -7367,58 +7368,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1204198572323685</v>
+        <v>0.04161196027515368</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.05598668052877809</v>
+        <v>-0.06275733463056832</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.01059279431847393</v>
+        <v>-0.312100342724963</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.0007071954500480373</v>
+        <v>0.1231169123948054</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.02100642584196168</v>
+        <v>0.4665502048704659</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.01364522417153996</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.312100342724963</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.4652994336443077</v>
+        <v>-0.03082746164398809</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.03648365119369596</v>
+        <v>1.075393689637124</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>-0.312100342724963</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1078964420679487</v>
+        <v>0.5141917127874001</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2793372765439066</v>
+        <v>-0.03294549909631383</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2008010667837797</v>
+        <v>0.908823964771956</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.01059279431847393</v>
+        <v>-0.06371665664689741</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1335128087116944</v>
+        <v>-6.661338147750939e-16</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.5022640521121498</v>
+        <v>-3.33066907387547e-16</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.4232124571775223</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -7473,67 +7474,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.1145658085070207</v>
+        <v>0.04161196027515435</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.05046928681138718</v>
+        <v>-0.06275733463056765</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.115533569251825</v>
+        <v>0.1231169123948052</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1729444590617458</v>
+        <v>0.466550204870466</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9454191033138402</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.2382824194485824</v>
+        <v>-0.3121003427249628</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.1036687135184464</v>
+        <v>-0.03082746164398775</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7690714431767565</v>
+        <v>1.075393689637123</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.4632271027539783</v>
+        <v>0.5141917127874007</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.04820235099123316</v>
+        <v>-0.0329454990963135</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.862090488003121</v>
+        <v>0.9088239647719573</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.08016850348153992</v>
+        <v>-0.06371665664689741</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.1380400921268788</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1315105948250126</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.2382219735145982</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.01805370513029447</v>
+        <v>0.03469224071623001</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>-0.03079078136225011</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.01805370513029558</v>
+        <v>0.06756335042966111</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -7779,28 +7780,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003974677</v>
+        <v>0.06101703543393744</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.103821015825279</v>
+        <v>0.1799741913752893</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213005</v>
+        <v>0.2405796270435321</v>
       </c>
       <c r="O2" s="2" t="n">
+        <v>0.9746588693957114</v>
+      </c>
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="P2" t="b">
-        <v>0</v>
-      </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138072</v>
+        <v>-0.3098313187450099</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -7809,10 +7810,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922785</v>
+        <v>0.5373300241682997</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7821,7 +7822,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174769</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7867,49 +7868,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.01474881982114307</v>
+        <v>0.2930599188275502</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.01238246152936839</v>
+        <v>0.2186985464363551</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.103867108384541</v>
+        <v>0.1617038815488626</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.3059568480665255</v>
+        <v>0.244271120885344</v>
       </c>
       <c r="O3" s="2" t="n">
+        <v>0.9317738791423001</v>
+      </c>
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="P3" t="b">
-        <v>0</v>
-      </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2083486754324957</v>
+        <v>-0.3268135676014445</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.02043384461706754</v>
+        <v>-0.02460593955894141</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9292931988265379</v>
+        <v>1.054811272550568</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2445519253278838</v>
+        <v>0.9208050795385059</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.0321591706503529</v>
+        <v>0.2494422468446016</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.8553590429456704</v>
+        <v>1.713667649530219</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.07255193694871198</v>
+        <v>-0.1128970535188779</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -7961,58 +7962,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>-0.02335558522365555</v>
+        <v>0.09480060127513035</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.02100989850384682</v>
+        <v>0.03184073837926271</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.07028481312061448</v>
+        <v>0.1155318330023982</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.1720647483703307</v>
       </c>
       <c r="O4" s="2" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="P4" t="b">
-        <v>0</v>
-      </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>0.1036687135184475</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.6940712220239806</v>
+        <v>0.769071443176754</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.4372788934221374</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.06508110111248899</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.813799478447114</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.08016850348153992</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.008735605270678293</v>
+        <v>-0.1533257002755035</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.06661651939830704</v>
+        <v>0.1315105948250137</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.07064593815919196</v>
+        <v>-0.2517310013739348</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -8063,67 +8064,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.1204198572323685</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>0.05598668052877809</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.01059279431847393</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.0007071954500480373</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.0210064258419617</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>0.01364522417153996</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.4652994336443077</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.03648365119369596</v>
       </c>
       <c r="T5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1078964420679485</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.2793372765439067</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2008010667837793</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.01059279431847393</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.03008926388438549</v>
+        <v>-0.1335128087116944</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.270382684972595</v>
+        <v>0.5022640521121498</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1891504220977268</v>
+        <v>-0.4232124571775224</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.02618350124865576</v>
+        <v>0.3731056573317193</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.02059674313262327</v>
+        <v>-0.2713930824850518</v>
       </c>
     </row>
     <row r="6">
@@ -8173,73 +8174,73 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.02335558522365544</v>
+        <v>0.1145658085070207</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.02100989850384671</v>
+        <v>0.05046928681138718</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.07028481312061437</v>
+        <v>0.115533569251825</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.1729444590617458</v>
       </c>
       <c r="O6" s="2" t="n">
+        <v>0.9454191033138402</v>
+      </c>
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="P6" t="b">
-        <v>0</v>
-      </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485824</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>0.1036687135184464</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.6940712220239802</v>
+        <v>0.7690714431767565</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.4632271027539783</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.04820235099123316</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.862090488003121</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.08016850348153992</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.008735605270678182</v>
+        <v>-0.1380400921268788</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.06661651939830726</v>
+        <v>0.1315105948250126</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.07064593815919196</v>
+        <v>-0.2382219735145982</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0.01805370513029447</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0</v>
+        <v>0.01805370513029558</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.02618350124865576</v>
+        <v>0.3731056573317193</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.03868077373001721</v>
+        <v>-0.09817014575252636</v>
       </c>
     </row>
     <row r="7">
@@ -8285,68 +8286,64 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.2043375826494194</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>-0.2500945877601592</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>0.2359673144875147</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.1972033968639685</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.3268135676014445</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>-0.02460593955894141</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>1.054811272550568</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1819347198006422</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.2311769748723456</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.3385902734213445</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0</v>
+        <v>-0.07668379937247682</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.03008926388438549</v>
+        <v>-0.3846670167674614</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.270382684972595</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1891504220977268</v>
+        <v>-0.3846670167674615</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.02618350124865576</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>-0.02059674313262327</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8395,19 +8392,19 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.02335558522365544</v>
+        <v>-0.03394881166061836</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.02100989850384671</v>
+        <v>-0.08950454509499595</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.07028481312061437</v>
+        <v>0.1952303144959528</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.2151016248349985</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>1</v>
@@ -8416,53 +8413,49 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.3268135676014445</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>-0.02460593955894141</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.6940712220239802</v>
+        <v>1.054811272550568</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.4350425704471679</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.06653578094038048</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.8096375614233425</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.08016850348153992</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.008735605270678182</v>
+        <v>-0.2528952647334979</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.06661651939830726</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.07064593815919196</v>
+        <v>-0.2528952647334979</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.1176007875642308</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.1162256857571463</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>0.02618350124865576</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>0.03868077373001721</v>
-      </c>
+        <v>-0.001555942263679166</v>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8507,68 +8500,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.1204198572323685</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>0.05598668052877809</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>-0.01059279431847393</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>0.0007071954500480373</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.02100642584196168</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0</v>
+        <v>0.01364522417153996</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.4652994336443077</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.03648365119369596</v>
       </c>
       <c r="T9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1078964420679487</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.2793372765439066</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2008010667837797</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0</v>
+        <v>-0.01059279431847393</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.03008926388438549</v>
+        <v>-0.1335128087116944</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.270382684972595</v>
+        <v>0.5022640521121498</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1891504220977268</v>
+        <v>-0.4232124571775223</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.02618350124865576</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>-0.02059674313262327</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8617,74 +8606,70 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.02335558522365544</v>
+        <v>0.1145658085070207</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.02100989850384671</v>
+        <v>0.05046928681138718</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.07028481312061437</v>
+        <v>0.115533569251825</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.1729444590617458</v>
       </c>
       <c r="O10" s="2" t="n">
+        <v>0.9454191033138402</v>
+      </c>
+      <c r="P10" t="b">
         <v>1</v>
       </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485824</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>0.1036687135184464</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.6940712220239802</v>
+        <v>0.7690714431767565</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.4632271027539783</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.04820235099123316</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.862090488003121</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.08016850348153992</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.008735605270678182</v>
+        <v>-0.1380400921268788</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.06661651939830726</v>
+        <v>0.1315105948250126</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.07064593815919196</v>
+        <v>-0.2382219735145982</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0.01805370513029447</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.02618350124865576</v>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>0.03868077373001721</v>
-      </c>
+        <v>0.01805370513029558</v>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8697,7 +8682,1155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651873308</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947871</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138072</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490124</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>-0.01147991081539435</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.01632453182721105</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.2083486754324958</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.103295545269285</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.304269882301803</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.2083486754324957</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.02043384461706754</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.9292931988265379</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.2083486754324958</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.2486811535680242</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.03602230231600423</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.8420097505649996</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.07255193694871198</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>-0.02027479846139824</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-0.02507631676042987</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.06992591782126945</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.2355679791479366</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.08841159562168954</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0.6940712220239806</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.1602779293212004</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.1042692974226319</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.5426851908659128</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>-0.04423229897254077</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>-0.008897024696036704</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.06661651939830704</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.07079727598532048</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>0.02685499328949237</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.270382684972595</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.1916963247089252</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.02618350124865576</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.02059674313262327</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>-0.02027479846139812</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-0.02507631676042976</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.06992591782126936</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.2355679791479365</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.08841159562168954</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0.6940712220239802</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.1602779293212007</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.1042692974226318</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.5426851908659136</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>-0.04423229897254077</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>-0.008897024696036593</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.06661651939830726</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.07079727598532037</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.02618350124865576</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>0.03868077373001721</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>0.02685499328949237</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.270382684972595</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.1916963247089252</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.02618350124865576</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>-0.02059674313262327</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>-0.02027479846139812</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.02507631676042976</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.06992591782126936</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.2355679791479365</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.08841159562168954</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0.6940712220239802</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.1602779293212007</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.1042692974226318</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.5426851908659136</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>-0.04423229897254077</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>-0.008897024696036593</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.06661651939830726</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.07079727598532037</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>0.02618350124865576</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>0.03868077373001721</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>0.02685499328949237</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.270382684972595</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.1916963247089252</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.02618350124865576</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.02059674313262327</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>-0.02027479846139812</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>-0.02507631676042976</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.06992591782126936</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.2355679791479365</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0.08841159562168954</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.6940712220239802</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0.1602779293212007</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>-0.1042692974226318</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.5426851908659136</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>-0.04423229897254077</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>-0.008897024696036593</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0.06661651939830726</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>-0.07079727598532037</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.02618350124865576</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>0.03868077373001721</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8803,12 +9936,8 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>563</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
@@ -8817,10 +9946,10 @@
       </c>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.5562326869806095</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -8851,10 +9980,10 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>963</v>
+        <v>563</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -8864,7 +9993,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.9149709302325582</v>
+        <v>0.5568496949528563</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -8897,8 +10026,12 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>963</v>
+      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
@@ -8907,10 +10040,10 @@
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>0.9149709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8983,24 +10116,20 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-251</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>307</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="2" t="n">
-        <v>0.9766081871345029</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9031,21 +10160,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-251</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>307</v>
+      </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>251</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9062,30 +10193,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-30</v>
+      </c>
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -9115,15 +10248,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -9132,10 +10261,10 @@
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="2" t="n">
-        <v>0.3655523255813953</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9162,7 +10291,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
@@ -9171,16 +10300,14 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="2" t="n">
-        <v>0.5241379310344828</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9207,11 +10334,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
@@ -9220,10 +10351,10 @@
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>0.3655523255813953</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9250,7 +10381,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
@@ -9262,13 +10393,13 @@
         <v>1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4873294346978557</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -9295,22 +10426,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-30</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -9330,37 +10459,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>-193</v>
-      </c>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>57</v>
+      </c>
       <c r="J14" s="2" t="n">
-        <v>0.2770083102493075</v>
+        <v>0.4873294346978557</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -9377,37 +10504,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>209</v>
-      </c>
+        <v>-30</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.3670058139534884</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -9434,25 +10559,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-134</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>0.5241379310344828</v>
-      </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -9479,11 +10606,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-193</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -9492,10 +10623,10 @@
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0</v>
+        <v>0.2773155851358846</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -9522,14 +10653,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -9539,7 +10670,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.9766081871345029</v>
+        <v>0.3670058139534884</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -9569,30 +10700,165 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-30</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="2" t="n">
+        <v>0.5205479452054794</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>307</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
